--- a/Output Data/GSR Data/20210510/20210525 cold gsr_ehsan.xlsx
+++ b/Output Data/GSR Data/20210510/20210525 cold gsr_ehsan.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Galvanic Skin Response Data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Galvanic Skin Response Data1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Galvanic Skin Response Data2" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5133,4 +5134,2362 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B292"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Time (Seconds)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Current (uAmps)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>0.32366</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>0.328238</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>0.3340340000000001</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>17.55</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>0.3390099999999999</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.342382</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>27.55</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>0.344844</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>0.3474</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>37.55</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>0.35032</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>42.55</v>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>0.353452</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>47.55</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>0.356842</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>52.55</v>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>0.359698</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>57.55</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>0.362326</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>62.55</v>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>0.3649579999999999</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>67.55</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>0.36719</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>0.3691480000000001</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>77.55</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>0.3703060000000001</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>82.55</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>0.37044</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>87.55</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>0.3708960000000001</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>92.55</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>0.371976</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>97.55</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>0.373876</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>102.55</v>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>0.375694</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>107.55</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>0.377252</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>112.55</v>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>0.377836</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>117.55</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>0.375356</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>122.55</v>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>0.375924</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>127.55</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>0.377084</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>132.55</v>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>0.378382</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>137.55</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>0.380084</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>142.55</v>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>0.381864</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>147.55</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>0.383318</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>152.55</v>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>0.3845140000000001</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>157.55</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>0.385744</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>162.55</v>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>0.386482</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>167.55</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>0.387104</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>172.55</v>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>0.3874460000000001</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>177.55</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>0.3877059999999999</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>182.55</v>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>0.387588</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>187.55</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>0.3866420000000001</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>192.55</v>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>0.38686</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>197.55</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>0.3877620000000001</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>202.55</v>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>0.3884920000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>207.55</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>0.389112</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>212.55</v>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>0.389848</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>217.55</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>0.390896</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>222.55</v>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>0.3917459999999999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>227.55</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>0.392784</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>232.55</v>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>0.394028</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>237.55</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>0.3950600000000001</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>242.55</v>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>0.3958099999999999</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>247.55</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>0.3974259999999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>252.55</v>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>0.397682</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>257.55</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>0.39839</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>262.55</v>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>0.3989040000000001</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>267.55</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>0.3993719999999999</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>272.55</v>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>0.40017</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>277.55</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>0.400788</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>282.55</v>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>0.4016339999999999</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>287.55</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>0.4029820000000001</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>292.55</v>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>0.40426</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>297.55</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>0.405342</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>302.55</v>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>0.4071040000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>307.55</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>0.407948</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>312.55</v>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>0.409778</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>317.55</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>0.411172</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>322.55</v>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>0.4129339999999999</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>327.55</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>0.4144700000000001</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>332.55</v>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>0.4165219999999999</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>337.55</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>0.419062</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>342.55</v>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>0.420678</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>347.55</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>0.4216220000000001</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>352.55</v>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>0.423156</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>357.55</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>0.424196</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>362.55</v>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>0.42461</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>367.55</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>0.4244959999999999</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>372.55</v>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>0.424014</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>377.55</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>0.4227</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>382.55</v>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>0.4199740000000001</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>387.55</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>0.417116</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>392.55</v>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>0.414578</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>397.55</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>0.4131320000000001</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>402.55</v>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>0.413236</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>407.55</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>0.413568</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>412.55</v>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>0.414124</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>417.55</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>0.4142280000000001</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>422.55</v>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>0.4142120000000001</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>427.55</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>0.414552</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>432.55</v>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>0.414768</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>437.55</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>0.415102</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>442.55</v>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>0.415382</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>447.55</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>0.415576</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>452.55</v>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>0.416286</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>457.55</v>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>0.417248</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>462.55</v>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>0.4180140000000001</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>467.55</v>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>0.4188939999999999</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>472.55</v>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>0.419774</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>477.55</v>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>0.420466</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>482.55</v>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>0.421452</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>487.55</v>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>0.422568</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>492.55</v>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>0.4236139999999999</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>497.55</v>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>0.4252319999999999</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>502.55</v>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>0.426028</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="n">
+        <v>507.55</v>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>0.42699</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="n">
+        <v>512.55</v>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>0.427916</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="n">
+        <v>517.55</v>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>0.4288980000000001</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="n">
+        <v>522.55</v>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>0.429702</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="n">
+        <v>527.55</v>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>0.431126</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="n">
+        <v>532.55</v>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>0.431632</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="n">
+        <v>537.55</v>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>0.432966</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="n">
+        <v>542.55</v>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>0.43403</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="n">
+        <v>547.55</v>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>0.435096</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="n">
+        <v>552.55</v>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>0.435956</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="n">
+        <v>557.55</v>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>0.436694</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="n">
+        <v>562.55</v>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>0.437564</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="n">
+        <v>567.55</v>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>0.438368</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="n">
+        <v>572.55</v>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>0.4392579999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>577.55</v>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>0.4403859999999999</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>582.55</v>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>0.441416</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>587.55</v>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>0.4423520000000001</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>592.55</v>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>0.4433219999999999</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>597.55</v>
+      </c>
+      <c r="B121" s="2" t="n">
+        <v>0.444178</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>602.55</v>
+      </c>
+      <c r="B122" s="2" t="n">
+        <v>0.444946</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>607.55</v>
+      </c>
+      <c r="B123" s="2" t="n">
+        <v>0.4456620000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>612.55</v>
+      </c>
+      <c r="B124" s="2" t="n">
+        <v>0.4464219999999999</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>617.55</v>
+      </c>
+      <c r="B125" s="2" t="n">
+        <v>0.447414</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>622.55</v>
+      </c>
+      <c r="B126" s="2" t="n">
+        <v>0.4484500000000001</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>627.55</v>
+      </c>
+      <c r="B127" s="2" t="n">
+        <v>0.449406</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>632.55</v>
+      </c>
+      <c r="B128" s="2" t="n">
+        <v>0.451276</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>637.55</v>
+      </c>
+      <c r="B129" s="2" t="n">
+        <v>0.4513159999999999</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>642.55</v>
+      </c>
+      <c r="B130" s="2" t="n">
+        <v>0.45223</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>647.55</v>
+      </c>
+      <c r="B131" s="2" t="n">
+        <v>0.453454</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>652.55</v>
+      </c>
+      <c r="B132" s="2" t="n">
+        <v>0.454996</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>657.55</v>
+      </c>
+      <c r="B133" s="2" t="n">
+        <v>0.4566</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>662.55</v>
+      </c>
+      <c r="B134" s="2" t="n">
+        <v>0.457246</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>667.55</v>
+      </c>
+      <c r="B135" s="2" t="n">
+        <v>0.458674</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>672.55</v>
+      </c>
+      <c r="B136" s="2" t="n">
+        <v>0.459844</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>677.55</v>
+      </c>
+      <c r="B137" s="2" t="n">
+        <v>0.4609500000000001</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>682.55</v>
+      </c>
+      <c r="B138" s="2" t="n">
+        <v>0.4619799999999999</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>687.55</v>
+      </c>
+      <c r="B139" s="2" t="n">
+        <v>0.4630779999999999</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>692.55</v>
+      </c>
+      <c r="B140" s="2" t="n">
+        <v>0.4643119999999999</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>697.55</v>
+      </c>
+      <c r="B141" s="2" t="n">
+        <v>0.46527</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>702.55</v>
+      </c>
+      <c r="B142" s="2" t="n">
+        <v>0.466206</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>707.55</v>
+      </c>
+      <c r="B143" s="2" t="n">
+        <v>0.467268</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="n">
+        <v>712.55</v>
+      </c>
+      <c r="B144" s="2" t="n">
+        <v>0.46822</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="n">
+        <v>717.55</v>
+      </c>
+      <c r="B145" s="2" t="n">
+        <v>0.469372</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="n">
+        <v>722.55</v>
+      </c>
+      <c r="B146" s="2" t="n">
+        <v>0.470584</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="n">
+        <v>727.55</v>
+      </c>
+      <c r="B147" s="2" t="n">
+        <v>0.47148</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="n">
+        <v>732.55</v>
+      </c>
+      <c r="B148" s="2" t="n">
+        <v>0.4723239999999999</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="n">
+        <v>737.55</v>
+      </c>
+      <c r="B149" s="2" t="n">
+        <v>0.473526</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="n">
+        <v>742.55</v>
+      </c>
+      <c r="B150" s="2" t="n">
+        <v>0.486876</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="n">
+        <v>747.55</v>
+      </c>
+      <c r="B151" s="2" t="n">
+        <v>0.5015419999999999</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="n">
+        <v>752.55</v>
+      </c>
+      <c r="B152" s="2" t="n">
+        <v>0.5008859999999999</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="n">
+        <v>757.55</v>
+      </c>
+      <c r="B153" s="2" t="n">
+        <v>0.5038419999999999</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="n">
+        <v>762.55</v>
+      </c>
+      <c r="B154" s="2" t="n">
+        <v>0.5069520000000001</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="n">
+        <v>767.55</v>
+      </c>
+      <c r="B155" s="2" t="n">
+        <v>0.507094</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="n">
+        <v>772.55</v>
+      </c>
+      <c r="B156" s="2" t="n">
+        <v>0.506826</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="n">
+        <v>777.55</v>
+      </c>
+      <c r="B157" s="2" t="n">
+        <v>0.507908</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="n">
+        <v>782.55</v>
+      </c>
+      <c r="B158" s="2" t="n">
+        <v>0.509378</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="n">
+        <v>787.55</v>
+      </c>
+      <c r="B159" s="2" t="n">
+        <v>0.511742</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="n">
+        <v>792.55</v>
+      </c>
+      <c r="B160" s="2" t="n">
+        <v>0.514474</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="n">
+        <v>797.55</v>
+      </c>
+      <c r="B161" s="2" t="n">
+        <v>0.516792</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="n">
+        <v>802.55</v>
+      </c>
+      <c r="B162" s="2" t="n">
+        <v>0.520366</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="n">
+        <v>807.5392156862747</v>
+      </c>
+      <c r="B163" s="2" t="n">
+        <v>0.5245960784313725</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="n">
+        <v>812.55</v>
+      </c>
+      <c r="B164" s="2" t="n">
+        <v>0.5261020000000001</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="n">
+        <v>817.55</v>
+      </c>
+      <c r="B165" s="2" t="n">
+        <v>0.5243180000000001</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="n">
+        <v>822.55</v>
+      </c>
+      <c r="B166" s="2" t="n">
+        <v>0.526958</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="n">
+        <v>827.55</v>
+      </c>
+      <c r="B167" s="2" t="n">
+        <v>0.525258</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="n">
+        <v>832.55</v>
+      </c>
+      <c r="B168" s="2" t="n">
+        <v>0.5335899999999999</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="n">
+        <v>837.55</v>
+      </c>
+      <c r="B169" s="2" t="n">
+        <v>0.534394</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="n">
+        <v>842.55</v>
+      </c>
+      <c r="B170" s="2" t="n">
+        <v>0.532846</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="n">
+        <v>847.55</v>
+      </c>
+      <c r="B171" s="2" t="n">
+        <v>0.5335539999999999</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="n">
+        <v>852.55</v>
+      </c>
+      <c r="B172" s="2" t="n">
+        <v>0.534368</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="n">
+        <v>857.55</v>
+      </c>
+      <c r="B173" s="2" t="n">
+        <v>0.534262</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="n">
+        <v>862.55</v>
+      </c>
+      <c r="B174" s="2" t="n">
+        <v>0.534324</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="n">
+        <v>867.55</v>
+      </c>
+      <c r="B175" s="2" t="n">
+        <v>0.5342060000000001</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="n">
+        <v>872.55</v>
+      </c>
+      <c r="B176" s="2" t="n">
+        <v>0.5344</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="n">
+        <v>877.55</v>
+      </c>
+      <c r="B177" s="2" t="n">
+        <v>0.53399</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="n">
+        <v>882.55</v>
+      </c>
+      <c r="B178" s="2" t="n">
+        <v>0.5340940000000001</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="n">
+        <v>887.55</v>
+      </c>
+      <c r="B179" s="2" t="n">
+        <v>0.5354059999999999</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="n">
+        <v>892.55</v>
+      </c>
+      <c r="B180" s="2" t="n">
+        <v>0.538314</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="n">
+        <v>897.55</v>
+      </c>
+      <c r="B181" s="2" t="n">
+        <v>0.537444</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="n">
+        <v>902.55</v>
+      </c>
+      <c r="B182" s="2" t="n">
+        <v>0.53471</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="n">
+        <v>907.55</v>
+      </c>
+      <c r="B183" s="2" t="n">
+        <v>0.5326960000000001</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="n">
+        <v>912.55</v>
+      </c>
+      <c r="B184" s="2" t="n">
+        <v>0.530226</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="2" t="n">
+        <v>917.55</v>
+      </c>
+      <c r="B185" s="2" t="n">
+        <v>0.5280940000000001</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="2" t="n">
+        <v>922.55</v>
+      </c>
+      <c r="B186" s="2" t="n">
+        <v>0.5265859999999999</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="2" t="n">
+        <v>927.55</v>
+      </c>
+      <c r="B187" s="2" t="n">
+        <v>0.525908</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="2" t="n">
+        <v>932.55</v>
+      </c>
+      <c r="B188" s="2" t="n">
+        <v>0.525766</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="2" t="n">
+        <v>937.55</v>
+      </c>
+      <c r="B189" s="2" t="n">
+        <v>0.52505</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="2" t="n">
+        <v>942.55</v>
+      </c>
+      <c r="B190" s="2" t="n">
+        <v>0.52547</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="n">
+        <v>947.55</v>
+      </c>
+      <c r="B191" s="2" t="n">
+        <v>0.525988</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="2" t="n">
+        <v>952.55</v>
+      </c>
+      <c r="B192" s="2" t="n">
+        <v>0.526772</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="2" t="n">
+        <v>957.55</v>
+      </c>
+      <c r="B193" s="2" t="n">
+        <v>0.5275279999999999</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="2" t="n">
+        <v>962.55</v>
+      </c>
+      <c r="B194" s="2" t="n">
+        <v>0.528266</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="2" t="n">
+        <v>967.55</v>
+      </c>
+      <c r="B195" s="2" t="n">
+        <v>0.529348</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="2" t="n">
+        <v>972.55</v>
+      </c>
+      <c r="B196" s="2" t="n">
+        <v>0.530292</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="B197" s="2" t="n">
+        <v>0.5301480000000001</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="2" t="n">
+        <v>982.55</v>
+      </c>
+      <c r="B198" s="2" t="n">
+        <v>0.530276</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="2" t="n">
+        <v>987.55</v>
+      </c>
+      <c r="B199" s="2" t="n">
+        <v>0.53084</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="2" t="n">
+        <v>992.55</v>
+      </c>
+      <c r="B200" s="2" t="n">
+        <v>0.5327499999999999</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="2" t="n">
+        <v>997.55</v>
+      </c>
+      <c r="B201" s="2" t="n">
+        <v>0.53339</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="2" t="n">
+        <v>1002.333333333333</v>
+      </c>
+      <c r="B202" s="2" t="n">
+        <v>0.534148888888889</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="2" t="n">
+        <v>1007.1</v>
+      </c>
+      <c r="B203" s="2" t="n">
+        <v>0.534772</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="2" t="n">
+        <v>1012.098039215686</v>
+      </c>
+      <c r="B204" s="2" t="n">
+        <v>0.5362764705882354</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="2" t="n">
+        <v>1017.1</v>
+      </c>
+      <c r="B205" s="2" t="n">
+        <v>0.5354479999999999</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="2" t="n">
+        <v>1022.1</v>
+      </c>
+      <c r="B206" s="2" t="n">
+        <v>0.5347260000000001</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="2" t="n">
+        <v>1027.1</v>
+      </c>
+      <c r="B207" s="2" t="n">
+        <v>0.53429</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="2" t="n">
+        <v>1032.1</v>
+      </c>
+      <c r="B208" s="2" t="n">
+        <v>0.5343600000000001</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="2" t="n">
+        <v>1037.1</v>
+      </c>
+      <c r="B209" s="2" t="n">
+        <v>0.535114</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="2" t="n">
+        <v>1042.1</v>
+      </c>
+      <c r="B210" s="2" t="n">
+        <v>0.5351859999999999</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="2" t="n">
+        <v>1047.1</v>
+      </c>
+      <c r="B211" s="2" t="n">
+        <v>0.5354079999999999</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="2" t="n">
+        <v>1052.1</v>
+      </c>
+      <c r="B212" s="2" t="n">
+        <v>0.5357780000000001</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="n">
+        <v>1057.1</v>
+      </c>
+      <c r="B213" s="2" t="n">
+        <v>0.5361440000000001</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="n">
+        <v>1062.1</v>
+      </c>
+      <c r="B214" s="2" t="n">
+        <v>0.53661</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="n">
+        <v>1067.1</v>
+      </c>
+      <c r="B215" s="2" t="n">
+        <v>0.5369</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="n">
+        <v>1072.1</v>
+      </c>
+      <c r="B216" s="2" t="n">
+        <v>0.5373660000000001</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="n">
+        <v>1077.1</v>
+      </c>
+      <c r="B217" s="2" t="n">
+        <v>0.537748</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="n">
+        <v>1082.1</v>
+      </c>
+      <c r="B218" s="2" t="n">
+        <v>0.5382439999999999</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="2" t="n">
+        <v>1087.1</v>
+      </c>
+      <c r="B219" s="2" t="n">
+        <v>0.5387240000000001</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="2" t="n">
+        <v>1092.1</v>
+      </c>
+      <c r="B220" s="2" t="n">
+        <v>0.5391720000000001</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="2" t="n">
+        <v>1097.1</v>
+      </c>
+      <c r="B221" s="2" t="n">
+        <v>0.5396499999999999</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="2" t="n">
+        <v>1102.1</v>
+      </c>
+      <c r="B222" s="2" t="n">
+        <v>0.5404420000000001</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>1107.1</v>
+      </c>
+      <c r="B223" s="2" t="n">
+        <v>0.541452</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
+        <v>1112.1</v>
+      </c>
+      <c r="B224" s="2" t="n">
+        <v>0.542258</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="2" t="n">
+        <v>1117.1</v>
+      </c>
+      <c r="B225" s="2" t="n">
+        <v>0.5430560000000001</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="n">
+        <v>1122.1</v>
+      </c>
+      <c r="B226" s="2" t="n">
+        <v>0.5437679999999999</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="2" t="n">
+        <v>1127.1</v>
+      </c>
+      <c r="B227" s="2" t="n">
+        <v>0.5443979999999999</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="n">
+        <v>1132.1</v>
+      </c>
+      <c r="B228" s="2" t="n">
+        <v>0.5447679999999998</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="n">
+        <v>1137.1</v>
+      </c>
+      <c r="B229" s="2" t="n">
+        <v>0.5447299999999999</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="n">
+        <v>1142.1</v>
+      </c>
+      <c r="B230" s="2" t="n">
+        <v>0.5438319999999999</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="n">
+        <v>1147.1</v>
+      </c>
+      <c r="B231" s="2" t="n">
+        <v>0.5432819999999999</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="n">
+        <v>1152.1</v>
+      </c>
+      <c r="B232" s="2" t="n">
+        <v>0.5430980000000001</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="n">
+        <v>1157.1</v>
+      </c>
+      <c r="B233" s="2" t="n">
+        <v>0.5430779999999999</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="n">
+        <v>1162.1</v>
+      </c>
+      <c r="B234" s="2" t="n">
+        <v>0.543618</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="2" t="n">
+        <v>1167.1</v>
+      </c>
+      <c r="B235" s="2" t="n">
+        <v>0.5443479999999999</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="n">
+        <v>1172.1</v>
+      </c>
+      <c r="B236" s="2" t="n">
+        <v>0.545084</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="n">
+        <v>1177.1</v>
+      </c>
+      <c r="B237" s="2" t="n">
+        <v>0.545636</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="n">
+        <v>1182.1</v>
+      </c>
+      <c r="B238" s="2" t="n">
+        <v>0.546688</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="n">
+        <v>1187.1</v>
+      </c>
+      <c r="B239" s="2" t="n">
+        <v>0.5474180000000001</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="n">
+        <v>1192.1</v>
+      </c>
+      <c r="B240" s="2" t="n">
+        <v>0.548238</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="2" t="n">
+        <v>1197.1</v>
+      </c>
+      <c r="B241" s="2" t="n">
+        <v>0.549288</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="n">
+        <v>1202.1</v>
+      </c>
+      <c r="B242" s="2" t="n">
+        <v>0.550322</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="n">
+        <v>1207.1</v>
+      </c>
+      <c r="B243" s="2" t="n">
+        <v>0.551354</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="n">
+        <v>1212.1</v>
+      </c>
+      <c r="B244" s="2" t="n">
+        <v>0.552392</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="n">
+        <v>1217.1</v>
+      </c>
+      <c r="B245" s="2" t="n">
+        <v>0.5535380000000001</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="n">
+        <v>1222.1</v>
+      </c>
+      <c r="B246" s="2" t="n">
+        <v>0.554764</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="n">
+        <v>1227.1</v>
+      </c>
+      <c r="B247" s="2" t="n">
+        <v>0.555498</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="n">
+        <v>1232.1</v>
+      </c>
+      <c r="B248" s="2" t="n">
+        <v>0.556378</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="n">
+        <v>1237.1</v>
+      </c>
+      <c r="B249" s="2" t="n">
+        <v>0.557408</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="n">
+        <v>1242.1</v>
+      </c>
+      <c r="B250" s="2" t="n">
+        <v>0.5581499999999999</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="n">
+        <v>1247.1</v>
+      </c>
+      <c r="B251" s="2" t="n">
+        <v>0.559056</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="n">
+        <v>1252.1</v>
+      </c>
+      <c r="B252" s="2" t="n">
+        <v>0.560042</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="n">
+        <v>1257.1</v>
+      </c>
+      <c r="B253" s="2" t="n">
+        <v>0.5610059999999999</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="n">
+        <v>1262.1</v>
+      </c>
+      <c r="B254" s="2" t="n">
+        <v>0.562192</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="n">
+        <v>1267.1</v>
+      </c>
+      <c r="B255" s="2" t="n">
+        <v>0.56334</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="n">
+        <v>1272.1</v>
+      </c>
+      <c r="B256" s="2" t="n">
+        <v>0.5649339999999999</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="n">
+        <v>1277.1</v>
+      </c>
+      <c r="B257" s="2" t="n">
+        <v>0.5666359999999999</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="n">
+        <v>1282.1</v>
+      </c>
+      <c r="B258" s="2" t="n">
+        <v>0.5684819999999999</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="n">
+        <v>1287.1</v>
+      </c>
+      <c r="B259" s="2" t="n">
+        <v>0.569726</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="n">
+        <v>1292.1</v>
+      </c>
+      <c r="B260" s="2" t="n">
+        <v>0.5708860000000001</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="n">
+        <v>1297.1</v>
+      </c>
+      <c r="B261" s="2" t="n">
+        <v>0.571862</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="n">
+        <v>1302.1</v>
+      </c>
+      <c r="B262" s="2" t="n">
+        <v>0.5730999999999999</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="n">
+        <v>1307.1</v>
+      </c>
+      <c r="B263" s="2" t="n">
+        <v>0.574712</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="n">
+        <v>1312.1</v>
+      </c>
+      <c r="B264" s="2" t="n">
+        <v>0.575612</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="n">
+        <v>1317.1</v>
+      </c>
+      <c r="B265" s="2" t="n">
+        <v>0.5774819999999999</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="n">
+        <v>1322.1</v>
+      </c>
+      <c r="B266" s="2" t="n">
+        <v>0.57856</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="n">
+        <v>1327.1</v>
+      </c>
+      <c r="B267" s="2" t="n">
+        <v>0.579274</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="n">
+        <v>1332.1</v>
+      </c>
+      <c r="B268" s="2" t="n">
+        <v>0.5803720000000001</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="2" t="n">
+        <v>1337.1</v>
+      </c>
+      <c r="B269" s="2" t="n">
+        <v>0.58181</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="2" t="n">
+        <v>1342.1</v>
+      </c>
+      <c r="B270" s="2" t="n">
+        <v>0.582556</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="2" t="n">
+        <v>1347.1</v>
+      </c>
+      <c r="B271" s="2" t="n">
+        <v>0.583538</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="2" t="n">
+        <v>1352.1</v>
+      </c>
+      <c r="B272" s="2" t="n">
+        <v>0.584674</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>1357.1</v>
+      </c>
+      <c r="B273" s="2" t="n">
+        <v>0.585518</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="2" t="n">
+        <v>1362.1</v>
+      </c>
+      <c r="B274" s="2" t="n">
+        <v>0.5865459999999999</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="2" t="n">
+        <v>1367.1</v>
+      </c>
+      <c r="B275" s="2" t="n">
+        <v>0.587162</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="2" t="n">
+        <v>1372.1</v>
+      </c>
+      <c r="B276" s="2" t="n">
+        <v>0.588132</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2" t="n">
+        <v>1377.1</v>
+      </c>
+      <c r="B277" s="2" t="n">
+        <v>0.5889300000000001</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2" t="n">
+        <v>1382.1</v>
+      </c>
+      <c r="B278" s="2" t="n">
+        <v>0.589876</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2" t="n">
+        <v>1387.1</v>
+      </c>
+      <c r="B279" s="2" t="n">
+        <v>0.5911279999999999</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2" t="n">
+        <v>1392.1</v>
+      </c>
+      <c r="B280" s="2" t="n">
+        <v>0.592368</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2" t="n">
+        <v>1397.1</v>
+      </c>
+      <c r="B281" s="2" t="n">
+        <v>0.59321</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2" t="n">
+        <v>1402.1</v>
+      </c>
+      <c r="B282" s="2" t="n">
+        <v>0.59415</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2" t="n">
+        <v>1407.1</v>
+      </c>
+      <c r="B283" s="2" t="n">
+        <v>0.5950660000000001</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2" t="n">
+        <v>1412.1</v>
+      </c>
+      <c r="B284" s="2" t="n">
+        <v>0.5957819999999999</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2" t="n">
+        <v>1417.1</v>
+      </c>
+      <c r="B285" s="2" t="n">
+        <v>0.59661</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2" t="n">
+        <v>1422.098039215686</v>
+      </c>
+      <c r="B286" s="2" t="n">
+        <v>0.5980235294117647</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2" t="n">
+        <v>1427.1</v>
+      </c>
+      <c r="B287" s="2" t="n">
+        <v>0.599072</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2" t="n">
+        <v>1432.1</v>
+      </c>
+      <c r="B288" s="2" t="n">
+        <v>0.6000559999999999</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2" t="n">
+        <v>1437.1</v>
+      </c>
+      <c r="B289" s="2" t="n">
+        <v>0.6010300000000001</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2" t="n">
+        <v>1442.1</v>
+      </c>
+      <c r="B290" s="2" t="n">
+        <v>0.6019939999999999</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2" t="n">
+        <v>1447.1</v>
+      </c>
+      <c r="B291" s="2" t="n">
+        <v>0.6032299999999999</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2" t="n">
+        <v>1452.1</v>
+      </c>
+      <c r="B292" s="2" t="n">
+        <v>0.604356</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>